--- a/target/test-classes/data/Admin_Data.xlsx
+++ b/target/test-classes/data/Admin_Data.xlsx
@@ -1,21 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Zalo\DATN\Automation_AFF\src\test\resources\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1004439C-7742-4F1C-B7D3-EB06B590109D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="330" yWindow="-120" windowWidth="28590" windowHeight="16440" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Login"/>
-    <sheet r:id="rId2" sheetId="2" name="UpCategory"/>
-    <sheet r:id="rId3" sheetId="3" name="AdCategory"/>
-    <sheet r:id="rId4" sheetId="4" name="Search"/>
-    <sheet r:id="rId5" sheetId="5" name="SCart"/>
-    <sheet r:id="rId6" sheetId="6" name="Order"/>
-    <sheet r:id="rId7" sheetId="7" name="Information"/>
+    <sheet name="Login" sheetId="1" r:id="rId1"/>
+    <sheet name="Brand" sheetId="3" r:id="rId2"/>
+    <sheet name="Product" sheetId="2" r:id="rId3"/>
+    <sheet name="Author" sheetId="4" r:id="rId4"/>
+    <sheet name="Tree" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -118,8 +122,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -169,41 +172,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -214,10 +211,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -255,71 +252,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -347,7 +344,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -370,11 +367,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -383,13 +380,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -399,7 +396,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -408,7 +405,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -417,7 +414,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -425,10 +422,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -493,58 +490,58 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="5" width="24.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="17.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="33.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="5" width="24.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="8" width="41.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="5" width="30.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" t="s">
         <v>30</v>
       </c>
     </row>
@@ -554,65 +551,65 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="5" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="32.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="5" width="46.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="5" width="34.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="8" width="59.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="5" width="36.86214285714286" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="59" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" t="s">
         <v>23</v>
       </c>
     </row>
@@ -622,65 +619,64 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="5" width="11.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="15.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="18.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="5" width="36.86214285714286" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="5" width="6.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="8" width="59.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="5" width="13.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="1" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="46.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="59" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" t="s">
         <v>23</v>
       </c>
     </row>
@@ -690,22 +686,22 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="4" width="4.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="20.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="37.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="5" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="5" width="41.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="5" width="33.86214285714286" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="4" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row r="1" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -725,131 +721,85 @@
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    <row r="2" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
+      <c r="F2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+    <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3" t="s">
+      <c r="F3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+    <row r="4" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3" t="s">
+      <c r="F4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+    <row r="5" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3" t="s">
+      <c r="F5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+    <row r="6" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3" t="s">
+      <c r="F6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+    <row r="7" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3" t="s">
+      <c r="F7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+    <row r="8" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3" t="s">
+      <c r="F8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+    <row r="9" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+    </row>
+    <row r="10" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+    </row>
+    <row r="11" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+    </row>
+    <row r="12" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -857,31 +807,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>

--- a/target/test-classes/data/Admin_Data.xlsx
+++ b/target/test-classes/data/Admin_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Zalo\DATN\Automation_AFF\src\test\resources\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1004439C-7742-4F1C-B7D3-EB06B590109D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED486B2D-775C-4E09-A3E4-3F08197A3DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="-120" windowWidth="28590" windowHeight="16440" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="330" yWindow="-120" windowWidth="28590" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -24,10 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="31">
-  <si>
-    <t>STT</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="54">
   <si>
     <t>Search</t>
   </si>
@@ -117,13 +114,85 @@
   </si>
   <si>
     <t>Tài khoản đăng nhập thành cong</t>
+  </si>
+  <si>
+    <t>Email người dùng không tồn tại!</t>
+  </si>
+  <si>
+    <t>Bạn không có quyền</t>
+  </si>
+  <si>
+    <t>Email không hợp lệ.</t>
+  </si>
+  <si>
+    <t>Vui lòng nhập email</t>
+  </si>
+  <si>
+    <t>Để trống email</t>
+  </si>
+  <si>
+    <t>Nhập email bằng ký tự trắng</t>
+  </si>
+  <si>
+    <t>Nhập email nhưng có ký tự trắng (Đầu)</t>
+  </si>
+  <si>
+    <t>Nhập email nhưng có ký tự trắng (Giữa)</t>
+  </si>
+  <si>
+    <t>Nhập email nhưng có ký tự trắng (Cuối)</t>
+  </si>
+  <si>
+    <t>Nhập email sai định dạng (Không có @)</t>
+  </si>
+  <si>
+    <t>Nhập email sai định dạng (Thiếu tên miền)</t>
+  </si>
+  <si>
+    <t>Nhập email không tồn tại trong CSDL</t>
+  </si>
+  <si>
+    <t>Để trống mật khẩu</t>
+  </si>
+  <si>
+    <t>Nhập mật khẩu bằng ký tự trắng</t>
+  </si>
+  <si>
+    <t>Nhập mật khẩu sai</t>
+  </si>
+  <si>
+    <t>Nhập email không có quyền</t>
+  </si>
+  <si>
+    <t>Vui lòng nhập mật khẩu</t>
+  </si>
+  <si>
+    <t>Tài khoản hoặc mật khẩu người dùng không chính xác!</t>
+  </si>
+  <si>
+    <t>http://localhost:4200/admin/auth/login</t>
+  </si>
+  <si>
+    <t>TestType</t>
+  </si>
+  <si>
+    <t>Success</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Name_1</t>
+  </si>
+  <si>
+    <t>Name_2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,6 +211,29 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Times New Roman"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -172,7 +264,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -187,6 +279,22 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -494,55 +602,266 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C3" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C9" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C10" s="7" t="s">
         <v>30</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C11" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C12" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -555,7 +874,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
@@ -567,50 +886,53 @@
     <col min="7" max="7" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
         <v>14</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H1" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" t="s">
         <v>22</v>
-      </c>
-      <c r="G2" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -636,49 +958,29 @@
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
         <v>14</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>17</v>
-      </c>
     </row>
     <row r="2" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" t="s">
-        <v>23</v>
-      </c>
+      <c r="F2" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -690,10 +992,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
@@ -701,8 +1003,8 @@
     <col min="6" max="6" width="33.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -717,88 +1019,64 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
       <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
+    </row>
+    <row r="3" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3"/>
+      <c r="E3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="F3" t="s">
+    <row r="4" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4"/>
+      <c r="E4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="F4" t="s">
+    <row r="5" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5"/>
+      <c r="E5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="F5" t="s">
+    <row r="6" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6"/>
+      <c r="E6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
+    <row r="7" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7"/>
+      <c r="E7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
+    <row r="8" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8"/>
+      <c r="E8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+    </row>
+    <row r="10" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
     </row>
   </sheetData>
@@ -811,9 +1089,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>